--- a/sorties/analyse_hypotheses_depart/ze/analyse_hypotheses_depart.xlsx
+++ b/sorties/analyse_hypotheses_depart/ze/analyse_hypotheses_depart.xlsx
@@ -7,28 +7,29 @@
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 Hypothèses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2a Volume" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2b Par âge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2c Seniors" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2d Par catégorie" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3a Métiers volume" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3b Métiers part" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3c Métiers de la liste" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3d Noyau dur" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="4a Régions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="4b Départements" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="4c Exposition régions" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="4d Liste x régions" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="4e Seniors par territoire" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="5 Priorités" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Paramètres" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Définitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1 Hypothèses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2a Volume" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2b Par âge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2c Seniors" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2d Par catégorie" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3a Métiers volume" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3b Métiers part" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3c Métiers de la liste" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3d Noyau dur" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="4a Régions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="4b Départements" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="4c Exposition régions" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="4d Liste x régions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="4e Seniors par territoire" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="5 Priorités" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Paramètres" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="332">
   <si>
     <t xml:space="preserve">Hypothèses de départ 2024 → 2030 : analyse prête pour une note</t>
   </si>
@@ -111,13 +112,235 @@
     <t xml:space="preserve">5 Priorités : Priorités : métier, territoire, levier (non produit, voir la feuille)</t>
   </si>
   <si>
+    <t xml:space="preserve">Définitions : le sens de chaque colonne (à lire en premier).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paramètres : valeurs de configuration utilisées.</t>
   </si>
   <si>
+    <t xml:space="preserve">Terme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Définition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feuilles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salariés (du champ, du métier, de la catégorie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de salariés présents à la date de la photo BTS (2024) dans le champ : entreprises du périmètre Base, âge minimum de la configuration. C’est le dénominateur de la part susceptible de partir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Départs attendus (central)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de salariés qui devraient avoir quitté définitivement l’emploi entre 2024 et 2030 (retraite ou fin de carrière, invalidité, décès). C’est une espérance : la somme des probabilités individuelles de départ, pas un décompte de personnes identifiées. Les mobilités vers un autre employeur ne sont pas comptées : le nombre est un minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 3, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothèse basse (départs retardés) / Hypothèse haute (départs avancés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Même nombre de départs sous deux hypothèses de calendrier : la basse décale les âges de départ plus tard (moins de départs), la haute plus tôt (plus de départs). Le scénario central est entre les deux. Elles encadrent le résultat, elles ne sont pas des bornes d’erreur statistiques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part susceptible de partir (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Départs attendus divisés par les salariés du groupe (métier, catégorie, territoire), en %. Elle mesure la vitesse d’érosion d’un groupe, indépendamment de sa taille.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 3, 4, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Départs par an en moyenne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Départs attendus divisés par la durée de la plage (6 ans). Un ordre de grandeur à comparer à la capacité annuelle de recrutement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont retraite ou fin de carrière / dont invalidité / dont décès</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition des départs attendus entre les trois causes de sortie, au scénario central. La répartition est additive : la somme des trois redonne les départs attendus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poids dans l’ensemble des départs (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part des départs attendus du groupe dans tous les départs attendus du champ. Mesure ce que pèse le groupe dans l’effort de remplacement, indépendamment de sa vitesse d’érosion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rang par nombre de départs / Rang par part susceptible de partir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position du territoire parmi les territoires diffusés, 1 = le plus élevé. Deux classements distincts : par volume (combien il faut remplacer) et par part (à quelle vitesse). Un territoire peut être en tête de l’un et loin dans l’autre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a, 4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diffusé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« oui » quand la cellule respecte la règle de secret statistique ; « non diffusé (secret statistique) » sinon : ses valeurs sont vides, jamais zéro. Un territoire non diffusé n’est pas un territoire sans départ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seniors (55 ans et plus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salariés âgés de 55 ans et plus à la date de la photo BTS. La part des seniors mesure le vieillissement du groupe ; leurs départs sont les plus proches dans le temps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2c, 4e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code PCS / Métier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métier au sens de la nomenclature des professions et catégories socioprofessionnelles (PCS), à quatre caractères. Le libellé vient de la nomenclature officielle ; à défaut, « PCS &lt;code&gt; ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, 4d, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catégorie sociale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grande catégorie de la PCS : cadres, professions intermédiaires, employés, ouvriers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2d, 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Famille professionnelle (FAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regroupement de métiers utilisé par France Travail pour mesurer la tension. Chaque métier de la liste est rattaché à une famille ; c’est à ce niveau que la tension est connue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3c, 3d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En tension en France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« oui » si la famille professionnelle du métier a un rang de tension d’au moins 4 sur 5 en France (indicateur France Travail / Dares). La tension est une propriété nationale du métier : elle ne mesure jamais la tension d’un territoire. « inconnue » quand l’indicateur manque.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3c, 3d, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimension principale de la tension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parmi les sept composantes de la tension mesurées par France Travail (manque de main-d’œuvre disponible, formation spécifique au métier, conditions de travail contraignantes, faible attractivité salariale, inadéquation géographique, emplois peu durables, forte intensité d’embauche), celle qui pèse le plus pour la famille professionnelle du métier. Renseignée seulement pour un métier en tension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levier d’action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traduction opérationnelle de la dimension principale de la tension (par exemple « former tôt » pour une formation spécifique au métier). Il décrit la nature dominante de la difficulté de recrutement ; ce n’est pas une recommandation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3c, 3d, 4c, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confiance du rattachement PCS → FAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualité du lien entre le métier (PCS) et sa famille professionnelle (FAP), indiquée dans le classeur de la liste. « faible confiance » signale un rattachement incertain : la tension attribuée au métier est à lire avec réserve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croisement de la vitesse des départs du métier (rapides ou modérés, par rapport aux autres métiers de la liste) et de sa tension en France (en tension ou hors tension). Quatre situations ; « départs rapides et métier en tension » forme le noyau dur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noyau dur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les métiers de la liste en situation « départs rapides et métier en tension » : ceux où l’anticipation compte le plus, puisque les départs y sont rapides et les candidats difficiles à trouver.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3d, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil (typologie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil du département dans la typologie territoriale, qui croise le poids du département dans l’emploi du champ, le volume de ses départs et leur intensité (pôle majeur à renouveler rapidement, pôle majeur au renouvellement modéré, implantation stable, implantation réduite, situation à expertiser).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classe d’exposition aux remplacements difficiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sur 100 départs attendus dans les métiers de la liste du territoire, part de ceux qui concernent des métiers en tension en France, classée faible, modérée ou forte. « non diffusé » quand le secret ou une couverture insuffisante empêche la lecture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a, 4b, 4c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part des remplacements difficiles (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La même part, en valeur : départs attendus dans les métiers de la liste en tension divisés par les départs attendus dans tous les métiers de la liste du territoire. « France (%) » donne le repère national.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robustesse de la classe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« robuste » si la classe d’exposition ne change pas quand on fait varier les hypothèses (calendrier de départ, seuil de tension, rattachements de faible confiance) ; « à confirmer » sinon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Départs attendus dans les métiers suivis en tension (minimum)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de départs attendus dans les métiers de la première sous-liste en tension du territoire. C’est un minimum : les métiers hors liste ne sont pas observés sur cette dimension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écart à la France (points) / Lecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Différence, en points, entre la part susceptible de partir du métier dans le territoire et la même part en France. « plus forte qu’en France » à partir de 3,0 points, « plus faible » en deçà de l’opposé, « proche de la France » entre les deux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Région 1, 2, 3 (part %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour un métier du noyau dur, ses premières régions diffusées classées par part susceptible de partir décroissante, avec cette part entre parenthèses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hypothèses et critères de la projection 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaque hypothèse, sa valeur retenue, sa source et le sens dans lequel elle tire le résultat. Toutes les valeurs viennent de la configuration de la chaîne.</t>
+    <t xml:space="preserve">Chaque hypothèse, sa valeur retenue, sa source et le sens dans lequel elle tire le résultat. Toutes les valeurs viennent de la configuration de la chaîne. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Hypothèse</t>
@@ -303,7 +526,7 @@
     <t xml:space="preserve">Volume des départs attendus, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Scénario central encadré par les hypothèses basse (départs retardés) et haute (départs avancés). Décomposition par cause au scénario central.</t>
+    <t xml:space="preserve">Scénario central encadré par les hypothèses basse (départs retardés) et haute (départs avancés). Décomposition par cause au scénario central. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Indicateur</t>
@@ -312,10 +535,10 @@
     <t xml:space="preserve">Scénario central</t>
   </si>
   <si>
-    <t xml:space="preserve">Hypothèse basse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypothèse haute</t>
+    <t xml:space="preserve">Hypothèse basse (départs retardés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothèse haute (départs avancés)</t>
   </si>
   <si>
     <t xml:space="preserve">Salariés du champ</t>
@@ -324,12 +547,6 @@
     <t xml:space="preserve">Départs attendus entre 2024 et 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Part susceptible de partir (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Départs par an en moyenne</t>
-  </si>
-  <si>
     <t xml:space="preserve">dont retraite ou fin de carrière</t>
   </si>
   <si>
@@ -342,7 +559,7 @@
     <t xml:space="preserve">Départs attendus par tranche d’âge, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Âge à la date de la photo BTS. Une tranche non diffusée n’a aucune valeur (secret statistique).</t>
+    <t xml:space="preserve">Âge à la date de la photo BTS. Une tranche non diffusée n’a aucune valeur (secret statistique). Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Tranche d’âge</t>
@@ -351,15 +568,6 @@
     <t xml:space="preserve">Salariés</t>
   </si>
   <si>
-    <t xml:space="preserve">Départs attendus (central)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part des départs du champ (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diffusé</t>
-  </si>
-  <si>
     <t xml:space="preserve">45-48 ans</t>
   </si>
   <si>
@@ -378,7 +586,7 @@
     <t xml:space="preserve">Départs attendus : seniors et autres salariés, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Seniors = 55 ans et plus à la date de la photo BTS.</t>
+    <t xml:space="preserve">Seniors = 55 ans et plus à la date de la photo BTS. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">moins de 55 ans</t>
@@ -390,10 +598,7 @@
     <t xml:space="preserve">Départs attendus par grande catégorie sociale, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Table de diffusion nationale par catégorie (08d). Part susceptible de partir = départs / salariés de la catégorie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catégorie sociale</t>
+    <t xml:space="preserve">Table de diffusion nationale par catégorie (08d). Part susceptible de partir = départs / salariés de la catégorie. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Cadres</t>
@@ -411,7 +616,7 @@
     <t xml:space="preserve">Métiers portant le plus de départs, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Les 15 métiers (PCS) diffusés classés par départs attendus décroissants. Lecture : les chantiers de remplacement en masse.</t>
+    <t xml:space="preserve">Les 15 métiers (PCS) diffusés classés par départs attendus décroissants. Lecture : les chantiers de remplacement en masse. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Rang</t>
@@ -516,7 +721,7 @@
     <t xml:space="preserve">Métiers qui s’érodent le plus vite, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Les 15 métiers (PCS) d’au moins 50 salariés classés par part susceptible de partir décroissante. Lecture : les compétences en risque d’extinction.</t>
+    <t xml:space="preserve">Les 15 métiers (PCS) d’au moins 50 salariés classés par part susceptible de partir décroissante. Lecture : les compétences en risque d’extinction. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">5621</t>
@@ -528,7 +733,7 @@
     <t xml:space="preserve">Les métiers de la première sous-liste face aux départs et à la tension, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Situation = croisement de la vitesse des départs (part susceptible de partir) et de la tension nationale de la famille professionnelle (France Travail). La tension ne mesure jamais celle d’un territoire.</t>
+    <t xml:space="preserve">Situation = croisement de la vitesse des départs (part susceptible de partir) et de la tension nationale de la famille professionnelle (France Travail). La tension ne mesure jamais celle d’un territoire. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Note</t>
@@ -540,13 +745,13 @@
     <t xml:space="preserve">Noyau dur : départs rapides et métier en tension, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Métiers de la liste en situation « départs rapides et métier en tension », par part susceptible de partir décroissante, avec le levier dominant.</t>
+    <t xml:space="preserve">Métiers de la liste en situation « départs rapides et métier en tension », par part susceptible de partir décroissante, avec le levier dominant. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Départs attendus par région, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Total des catégories sociales diffusées ; une région dont une cellule est masquée n’est pas totalisée. Rang par volume et rang par part parmi les régions diffusées.</t>
+    <t xml:space="preserve">Total des catégories sociales diffusées ; une région dont une cellule est masquée n’est pas totalisée. Rang par volume et rang par part parmi les régions diffusées. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Non produit : diffusion par région (08d) absente : niveau non produit pour ce zonage.</t>
@@ -555,7 +760,7 @@
     <t xml:space="preserve">Départs attendus par département, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Même règle que les régions ; profil de la typologie et exposition aux remplacements difficiles quand ils sont diffusés. Un département non diffusé n’est pas un département sans départ.</t>
+    <t xml:space="preserve">Même règle que les régions ; profil de la typologie et exposition aux remplacements difficiles quand ils sont diffusés. Un département non diffusé n’est pas un département sans départ. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Non produit : diffusion par département (08d) absente : niveau non produit pour ce zonage.</t>
@@ -564,7 +769,7 @@
     <t xml:space="preserve">Exposition des régions aux remplacements difficiles</t>
   </si>
   <si>
-    <t xml:space="preserve">Part des départs des métiers suivis qui concernent des métiers en tension en France ; classe, robustesse de la classe, plancher de départs dans ces métiers.</t>
+    <t xml:space="preserve">Part des départs des métiers suivis qui concernent des métiers en tension en France ; classe, robustesse de la classe, plancher de départs dans ces métiers. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Non produit : exposition par région (08i) absente.</t>
@@ -573,7 +778,7 @@
     <t xml:space="preserve">Où les métiers de la première sous-liste partent plus vite qu’en France</t>
   </si>
   <si>
-    <t xml:space="preserve">Couples métier x région dont la part susceptible de partir dépasse celle de la France d’au moins 3,0 points, par écart décroissant.</t>
+    <t xml:space="preserve">Couples métier x région dont la part susceptible de partir dépasse celle de la France d’au moins 3,0 points, par écart décroissant. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Non produit : table métier x territoire (08j) absente.</t>
@@ -582,7 +787,7 @@
     <t xml:space="preserve">Seniors par Zone d'emploi, 2024 → 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Part des 55 ans et plus dans les salariés du champ et leurs départs attendus, par territoire du zonage d’analyse.</t>
+    <t xml:space="preserve">Part des 55 ans et plus dans les salariés du champ et leurs départs attendus, par territoire du zonage d’analyse. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -732,7 +937,7 @@
     <t xml:space="preserve">Priorités : métier, territoire, levier</t>
   </si>
   <si>
-    <t xml:space="preserve">Pour chaque métier du noyau dur : le levier dominant et ses 3 premières régions diffusées par part susceptible de partir.</t>
+    <t xml:space="preserve">Pour chaque métier du noyau dur : le levier dominant et ses 3 premières régions diffusées par part susceptible de partir. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
     <t xml:space="preserve">parametre</t>
@@ -802,9 +1007,6 @@
   </si>
   <si>
     <t xml:space="preserve">secret_min_salaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
   </si>
   <si>
     <t xml:space="preserve">secret_min_entreprises</t>
@@ -859,16 +1061,16 @@
       <b/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF52606D"/>
       <name val="Calibri"/>
       <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="3">
@@ -935,11 +1137,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1392,6 +1594,11 @@
         <v>27</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1407,23 +1614,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>169</v>
+      <c r="A1" s="5" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>170</v>
+      <c r="A2" s="6" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
+      <c r="A4" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -1441,23 +1648,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>171</v>
+      <c r="A1" s="5" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>172</v>
+      <c r="A2" s="6" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
+      <c r="A4" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -1475,23 +1682,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>174</v>
+      <c r="A1" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>175</v>
+      <c r="A2" s="6" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
+      <c r="A4" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>176</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -1505,27 +1712,27 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="45.21" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>177</v>
+      <c r="A1" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>178</v>
+      <c r="A2" s="6" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
+      <c r="A4" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>179</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -1539,27 +1746,27 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="48.61" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="45.21" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>180</v>
+      <c r="A1" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>181</v>
+      <c r="A2" s="6" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
+      <c r="A4" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>182</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -1569,6 +1776,40 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="48.61" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1584,47 +1825,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>183</v>
+      <c r="A1" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>184</v>
+      <c r="A2" s="6" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>109</v>
+      <c r="A4" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>165</v>
@@ -1642,15 +1883,15 @@
         <v>80.6</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>152</v>
@@ -1668,15 +1909,15 @@
         <v>78.6</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>158</v>
@@ -1694,15 +1935,15 @@
         <v>82.3</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>162</v>
@@ -1720,15 +1961,15 @@
         <v>82.3</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>169</v>
@@ -1746,15 +1987,15 @@
         <v>80.1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>156</v>
@@ -1772,15 +2013,15 @@
         <v>82.9</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>140</v>
@@ -1798,15 +2039,15 @@
         <v>79.7</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>119</v>
@@ -1824,15 +2065,15 @@
         <v>84.4</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>136</v>
@@ -1850,15 +2091,15 @@
         <v>86.5</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>146</v>
@@ -1876,15 +2117,15 @@
         <v>84</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>154</v>
@@ -1902,15 +2143,15 @@
         <v>80.9</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>156</v>
@@ -1928,15 +2169,15 @@
         <v>87.1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>154</v>
@@ -1954,15 +2195,15 @@
         <v>83.8</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>170</v>
@@ -1980,15 +2221,15 @@
         <v>83.1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>170</v>
@@ -2006,15 +2247,15 @@
         <v>82</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>131</v>
@@ -2032,15 +2273,15 @@
         <v>82.4</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>143</v>
@@ -2058,15 +2299,15 @@
         <v>82.1</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>128</v>
@@ -2084,15 +2325,15 @@
         <v>89.7</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>115</v>
@@ -2110,15 +2351,15 @@
         <v>82.2</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>129</v>
@@ -2136,15 +2377,15 @@
         <v>84.7</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>149</v>
@@ -2162,15 +2403,15 @@
         <v>79.6</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>126</v>
@@ -2188,15 +2429,15 @@
         <v>77.8</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>115</v>
@@ -2214,15 +2455,15 @@
         <v>87.5</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>158</v>
@@ -2240,15 +2481,15 @@
         <v>82.1</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>215</v>
+        <v>283</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>215</v>
+        <v>283</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>144</v>
@@ -2266,15 +2507,15 @@
         <v>79.7</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>140</v>
@@ -2292,15 +2533,15 @@
         <v>86.6</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>134</v>
@@ -2318,15 +2559,15 @@
         <v>83.2</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>218</v>
+        <v>286</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>218</v>
+        <v>286</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>141</v>
@@ -2344,15 +2585,15 @@
         <v>79.8</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>139</v>
@@ -2370,15 +2611,15 @@
         <v>85.5</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>109</v>
@@ -2396,15 +2637,15 @@
         <v>84.2</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>110</v>
@@ -2422,15 +2663,15 @@
         <v>79.9</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="s">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>118</v>
@@ -2448,15 +2689,15 @@
         <v>88.8</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>223</v>
+        <v>291</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>223</v>
+        <v>291</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>119</v>
@@ -2474,15 +2715,15 @@
         <v>86.6</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>95</v>
@@ -2500,15 +2741,15 @@
         <v>82.5</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>109</v>
@@ -2526,15 +2767,15 @@
         <v>81.7</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>226</v>
+        <v>294</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>226</v>
+        <v>294</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>105</v>
@@ -2552,15 +2793,15 @@
         <v>85.4</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>115</v>
@@ -2578,15 +2819,15 @@
         <v>83.8</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="s">
-        <v>228</v>
+        <v>296</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>228</v>
+        <v>296</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>128</v>
@@ -2604,15 +2845,15 @@
         <v>81.3</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>124</v>
@@ -2630,15 +2871,15 @@
         <v>87.4</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>103</v>
@@ -2656,15 +2897,15 @@
         <v>83.6</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>101</v>
@@ -2682,15 +2923,15 @@
         <v>83.8</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>87</v>
@@ -2708,41 +2949,7 @@
         <v>87.2</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2756,136 +2963,170 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
     <col min="1" max="1" width="34.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>236</v>
+      <c r="A1" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="B13" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>262</v>
+        <v>329</v>
       </c>
       <c r="B15" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>264</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2895,6 +3136,319 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="100.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2907,362 +3461,235 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>28</v>
+      <c r="A1" s="5" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>29</v>
+      <c r="A2" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>34</v>
+      <c r="A4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="32.46" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.31" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.46" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.46" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>5622</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>5622</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>5622</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>2079</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1965</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>39.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>346</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>328</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>1849</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>152</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+        <v>163</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3275,203 +3702,121 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="13.76" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="24.81" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.46" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.46" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="28.21" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="29.91" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.46" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="11.21" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="27.36" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="9.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="32.46" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.31" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="31.61" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="30.76" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>103</v>
+      <c r="A1" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>104</v>
+      <c r="A2" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>109</v>
+      <c r="A4" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>1610</v>
+        <v>170</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>5622</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>69</v>
+        <v>5622</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>111</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>2028</v>
+        <v>171</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>2079</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>365</v>
+        <v>1965</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>313</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>425</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>242</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>111</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>1335</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>1004</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>946</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>1057</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>964</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>111</v>
+        <v>40</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>39.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>649</v>
+        <v>43</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>346</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>641</v>
+        <v>328</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>638</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>643</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>640</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>111</v>
-      </c>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1849</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3484,132 +3829,202 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.46" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="13.76" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24.81" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.46" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.46" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="31.61" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="30.76" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.21" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="29.91" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.46" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="11.21" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="27.36" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="9.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>115</v>
+      <c r="A1" s="5" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>116</v>
+      <c r="A2" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>109</v>
+      <c r="A4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>117</v>
+      <c r="A5" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>3638</v>
+        <v>1610</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>434</v>
+        <v>69</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>381</v>
+        <v>68</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>496</v>
+        <v>71</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>11.9</v>
+        <v>4.3</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>245</v>
+        <v>3</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>20.9</v>
+        <v>3.3</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>118</v>
+      <c r="A6" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1984</v>
+        <v>2028</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1645</v>
+        <v>365</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1584</v>
+        <v>313</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1701</v>
+        <v>425</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>82.9</v>
+        <v>18</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1604</v>
+        <v>242</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="I6" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>946</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1057</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>964</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="I7" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="n">
-        <v>79.1</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>111</v>
+      <c r="J7" s="9" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>649</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>641</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>638</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>643</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3623,202 +4038,132 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.81" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.46" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24.81" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.46" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.46" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="31.61" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="30.76" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.21" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="29.91" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.46" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="11.21" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="27.36" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="9.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>119</v>
+      <c r="A1" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>120</v>
+      <c r="A2" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>109</v>
+      <c r="A4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>122</v>
+      <c r="A5" s="8" t="s">
+        <v>186</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1396</v>
+        <v>3638</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>375</v>
+        <v>496</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25.1</v>
+        <v>11.9</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>16.8</v>
+        <v>20.9</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>123</v>
+      <c r="A6" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1488</v>
+        <v>1984</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>515</v>
+        <v>1645</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>486</v>
+        <v>1584</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>546</v>
+        <v>1701</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>34.6</v>
+        <v>82.9</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>456</v>
+        <v>1604</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>24.8</v>
+        <v>79.1</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>1083</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>448</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>424</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>472</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>403</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>1655</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>765</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>729</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>803</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>685</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3832,538 +4177,202 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.81" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.81" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="24.81" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.46" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.81" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="31.61" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="30.76" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="28.21" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="29.91" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.46" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="28.21" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="27.36" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.21" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="9.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>126</v>
+      <c r="A1" s="5" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>127</v>
+      <c r="A2" s="6" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>108</v>
+      <c r="A4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>125</v>
+      <c r="A5" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>1396</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>326</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>362</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>164</v>
+        <v>375</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>25.1</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>156</v>
+        <v>304</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>172</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>45.2</v>
+        <v>22</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.9</v>
+        <v>16.8</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>125</v>
+      <c r="A6" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1488</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>515</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>486</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>316</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>152</v>
+        <v>546</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>34.6</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>146</v>
+        <v>456</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>48.2</v>
+        <v>38</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>7.3</v>
+        <v>24.8</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>125</v>
+      <c r="A7" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>1083</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>448</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>424</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>152</v>
+        <v>472</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>41.4</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>146</v>
+        <v>403</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>159</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>45.3</v>
+        <v>31</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>7.3</v>
+        <v>21.6</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>125</v>
+      <c r="A8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>1655</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>765</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>729</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>308</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>148</v>
+        <v>803</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>46.2</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>141</v>
+        <v>685</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>48.2</v>
+        <v>62</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>333</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>314</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>108</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>307</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>289</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>309</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>230</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>233</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>209</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>269</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>277</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>3.8</v>
+        <v>36.8</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -4383,52 +4392,52 @@
     <col min="4" max="4" width="24.81" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="24.81" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.46" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.46" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="31.61" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="30.76" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="28.21" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="27.36" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>161</v>
+      <c r="A1" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>162</v>
+      <c r="A2" s="6" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>108</v>
+      <c r="A4" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -4436,31 +4445,31 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>48.2</v>
+        <v>45.2</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
@@ -4468,31 +4477,31 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>48.2</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7">
@@ -4500,13 +4509,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>336</v>
@@ -4532,31 +4541,31 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>132</v>
+        <v>206</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="G8" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>156</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>172</v>
-      </c>
       <c r="I8" s="9" t="n">
-        <v>45.2</v>
+        <v>48.2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
@@ -4564,13 +4573,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>333</v>
@@ -4596,31 +4605,31 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>209</v>
+        <v>314</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>44.3</v>
+        <v>36.5</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
@@ -4628,31 +4637,31 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>43.1</v>
+        <v>34</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -4660,31 +4669,31 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>41.1</v>
+        <v>35.6</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -4692,31 +4701,31 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>40.8</v>
+        <v>33.2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="14">
@@ -4724,31 +4733,31 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>37.4</v>
+        <v>43.1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="15">
@@ -4756,31 +4765,31 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>141</v>
+        <v>219</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>314</v>
+        <v>233</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>36.5</v>
+        <v>40.8</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -4788,31 +4797,31 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>145</v>
+        <v>221</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>289</v>
+        <v>209</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>35.6</v>
+        <v>44.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17">
@@ -4820,31 +4829,31 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>307</v>
+        <v>269</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="18">
@@ -4852,31 +4861,31 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>33.8</v>
+        <v>41.1</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -4884,31 +4893,31 @@
         <v>15</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>148</v>
+        <v>228</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>33.2</v>
+        <v>28.6</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -4922,27 +4931,538 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.81" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="24.81" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="31.61" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="30.76" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="28.21" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>165</v>
+      <c r="A1" s="5" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>166</v>
+      <c r="A2" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>167</v>
+      <c r="A4" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>168</v>
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>316</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>308</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>362</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>172</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>333</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>209</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>314</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>289</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>307</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>269</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>309</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>

--- a/sorties/analyse_hypotheses_depart/ze/analyse_hypotheses_depart.xlsx
+++ b/sorties/analyse_hypotheses_depart/ze/analyse_hypotheses_depart.xlsx
@@ -8,28 +8,29 @@
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Définitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1 Hypothèses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2a Volume" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2b Par âge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2c Seniors" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2d Par catégorie" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3a Métiers volume" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3b Métiers part" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3c Métiers de la liste" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="3d Noyau dur" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="4a Régions" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="4b Départements" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="4c Exposition régions" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="4d Liste x régions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="4e Seniors par territoire" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="5 Priorités" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Paramètres" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Faits" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1 Hypothèses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2a Volume" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2b Par âge" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2c Seniors" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2d Par catégorie" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3a Métiers volume" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3b Métiers part" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3c Métiers de la liste" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3d Noyau dur" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="4a Régions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="4b Départements" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="4c Exposition régions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="4d Liste x régions" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="4e Seniors par territoire" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="5 Priorités" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Paramètres" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
   <si>
     <t xml:space="preserve">Hypothèses de départ 2024 → 2030 : analyse prête pour une note</t>
   </si>
@@ -115,6 +116,9 @@
     <t xml:space="preserve">Définitions : le sens de chaque colonne (à lire en premier).</t>
   </si>
   <si>
+    <t xml:space="preserve">Faits : une quinzaine de phrases vraies, écrites par la chaîne à partir des tableaux, à reprendre telles quelles dans la rédaction ; chaque feuille porte aussi, en ligne 3, une phrase « Lecture : » qui lit sa première cellule.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paramètres : valeurs de configuration utilisées.</t>
   </si>
   <si>
@@ -160,15 +164,21 @@
     <t xml:space="preserve">2, 3, 4, 5</t>
   </si>
   <si>
+    <t xml:space="preserve">Emploi actuel, tous âges / Intensité du renouvellement (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emploi actuel tous âges = salariés de tous âges des établissements du périmètre à la date de la photo BTS (stock 01c). Intensité du renouvellement = départs attendus rapportés à cet emploi, en % : la même mesure que la typologie des départements, qui permet de relier les deux notes. Elle est plus faible que la part susceptible de partir, dont le dénominateur se limite aux salariés de l’âge minimum et plus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Départs par an en moyenne</t>
   </si>
   <si>
     <t xml:space="preserve">Départs attendus divisés par la durée de la plage (6 ans). Un ordre de grandeur à comparer à la capacité annuelle de recrutement.</t>
   </si>
   <si>
-    <t xml:space="preserve">2a</t>
-  </si>
-  <si>
     <t xml:space="preserve">dont retraite ou fin de carrière / dont invalidité / dont décès</t>
   </si>
   <si>
@@ -337,12 +347,69 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
+    <t xml:space="preserve">Rubrique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feuille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entre 2024 et 2030, 2 079 des 5 622 salariés du champ devraient avoir quitté définitivement l’emploi, soit 37,0 % ; entre 1 965 (hypothèse basse, départs retardés) et 2 197 (hypothèse haute, départs avancés) selon le calendrier des fins de carrière. Les mobilités vers un autre employeur ne sont pas comptées : ces volumes sont des minimums.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2a Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cela représente 346 départs par an en moyenne sur 6 ans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les fins de carrière expliquent 1 849 départs sur 2 079 (88,9 %) ; l’invalidité en ajoute 152 et le décès 78.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapportés à l’emploi actuel tous âges du périmètre (18 432 salariés), les départs attendus représentent une intensité de renouvellement de 11,3 %, la mesure utilisée par la typologie des départements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les 55 ans et plus représentent 35,3 % des salariés du champ et 79,1 % des départs attendus ; 82,9 % d’entre eux sont susceptibles de partir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2c Seniors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les ouvriers ont la part susceptible de partir la plus élevée (46,2 %) et les cadres la plus faible (25,1 %) ; les ouvriers pèsent le plus dans l’ensemble des départs (36,8 %).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2d Par catégorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Métiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les métiers portant le plus de départs attendus sont PCS 6234 (164), PCS 6821 (152), PCS 6543 (152) ; ensemble, 22,5 % de l’ensemble des départs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3a Métiers volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les métiers qui s’érodent le plus vite (au moins 50 salariés) sont PCS 6821 (48,2 % de 316 salariés), PCS 6210 (48,2 % de 308 salariés), PCS 6543 (45,3 % de 336 salariés).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3b Métiers part</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hypothèses et critères de la projection 2024 → 2030</t>
   </si>
   <si>
     <t xml:space="preserve">Chaque hypothèse, sa valeur retenue, sa source et le sens dans lequel elle tire le résultat. Toutes les valeurs viennent de la configuration de la chaîne. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : chaque ligne donne une hypothèse, la valeur retenue, sa source, le sens dans lequel elle tire le résultat et ce qui la fait varier.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hypothèse</t>
   </si>
   <si>
@@ -529,6 +596,9 @@
     <t xml:space="preserve">Scénario central encadré par les hypothèses basse (départs retardés) et haute (départs avancés). Décomposition par cause au scénario central. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : au scénario central, 2 079 salariés devraient avoir quitté définitivement l’emploi entre 2024 et 2030, soit 37,0 % des 5 622 salariés du champ ; entre 1 965 et 2 197 selon le calendrier des fins de carrière.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indicateur</t>
   </si>
   <si>
@@ -556,12 +626,21 @@
     <t xml:space="preserve">dont décès</t>
   </si>
   <si>
+    <t xml:space="preserve">Emploi actuel, tous âges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensité du renouvellement (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Départs attendus par tranche d’âge, 2024 → 2030</t>
   </si>
   <si>
     <t xml:space="preserve">Âge à la date de la photo BTS. Une tranche non diffusée n’a aucune valeur (secret statistique). Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : 1 610 salariés (45-48 ans) ; 69 départs attendus au scénario central, soit 4,3 % d’entre eux et 3,3 % de l’ensemble des départs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tranche d’âge</t>
   </si>
   <si>
@@ -589,6 +668,12 @@
     <t xml:space="preserve">Seniors = 55 ans et plus à la date de la photo BTS. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : 3 638 salariés (moins de 55 ans) ; 434 départs attendus au scénario central, soit 11,9 % d’entre eux et 20,9 % de l’ensemble des départs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe d’âge</t>
+  </si>
+  <si>
     <t xml:space="preserve">moins de 55 ans</t>
   </si>
   <si>
@@ -601,6 +686,9 @@
     <t xml:space="preserve">Table de diffusion nationale par catégorie (08d). Part susceptible de partir = départs / salariés de la catégorie. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : 1 396 salariés (cadres) ; 350 départs attendus au scénario central, soit 25,1 % d’entre eux et 16,8 % de l’ensemble des départs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cadres</t>
   </si>
   <si>
@@ -619,6 +707,9 @@
     <t xml:space="preserve">Les 15 métiers (PCS) diffusés classés par départs attendus décroissants. Lecture : les chantiers de remplacement en masse. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : PCS 6234 porte le plus de départs attendus : 164, soit 45,2 % de ses 362 salariés et 7,9 % de l’ensemble des départs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rang</t>
   </si>
   <si>
@@ -724,6 +815,9 @@
     <t xml:space="preserve">Les 15 métiers (PCS) d’au moins 50 salariés classés par part susceptible de partir décroissante. Lecture : les compétences en risque d’extinction. Définition des colonnes : feuille « Définitions ».</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture : PCS 6821 a la part susceptible de partir la plus élevée parmi les métiers d’au moins 50 salariés : 48,2 % de ses 316 salariés, soit 152 départs attendus.</t>
+  </si>
+  <si>
     <t xml:space="preserve">5621</t>
   </si>
   <si>
@@ -788,6 +882,9 @@
   </si>
   <si>
     <t xml:space="preserve">Part des 55 ans et plus dans les salariés du champ et leurs départs attendus, par territoire du zonage d’analyse. Définition des colonnes : feuille « Définitions ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : Versailles compte 78 salariés de 55 ans et plus, soit 47,3 % de ses salariés du champ ; 63 départs attendus parmi eux (80,6 %).</t>
   </si>
   <si>
     <t xml:space="preserve">Code</t>
@@ -1035,7 +1132,7 @@
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1071,6 +1168,11 @@
       <color rgb="FF52606D"/>
       <name val="Calibri"/>
       <i/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2933"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1126,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1142,6 +1244,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1599,6 +1702,11 @@
         <v>28</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1610,27 +1718,543 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.81" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="24.81" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="31.61" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="30.76" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="28.21" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>234</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>316</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>152</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>236</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>308</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>336</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>152</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>159</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>333</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>230</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>211</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>314</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>307</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>269</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>
@@ -1649,22 +2273,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>238</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>236</v>
+      <c r="A5" s="8" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -1683,22 +2312,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>240</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>241</v>
+      <c r="A5" s="8" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -1717,22 +2351,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>243</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>244</v>
+      <c r="A5" s="8" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -1746,27 +2385,32 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="45.21" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>246</v>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>247</v>
+      <c r="A5" s="8" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1780,27 +2424,32 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="48.61" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="45.21" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>249</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>250</v>
+      <c r="A5" s="8" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -1810,6 +2459,45 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="48.61" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1826,1164 +2514,1135 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>252</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="8" t="n">
+      <c r="A5" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>165</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>47.3</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="10" t="n">
         <v>80.6</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>180</v>
+      <c r="H5" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="C6" s="8" t="n">
+      <c r="A6" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="9" t="n">
         <v>152</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>45.4</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="10" t="n">
         <v>78.6</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>180</v>
+      <c r="H6" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="A7" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>158</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>44.9</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>82.3</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>180</v>
+      <c r="H7" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="8" t="n">
+      <c r="A8" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>162</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>44.4</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="10" t="n">
         <v>82.3</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>180</v>
+      <c r="H8" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="8" t="n">
+      <c r="A9" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>169</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>44.4</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>80.1</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>180</v>
+      <c r="H9" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="8" t="n">
+      <c r="A10" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="9" t="n">
         <v>156</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>42.9</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <v>82.9</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>180</v>
+      <c r="H10" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="A11" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>42.1</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="10" t="n">
         <v>79.7</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>180</v>
+      <c r="H11" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C12" s="8" t="n">
+      <c r="A12" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="10" t="n">
         <v>84.4</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>180</v>
+      <c r="H12" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C13" s="8" t="n">
+      <c r="A13" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="9" t="n">
         <v>136</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>41.9</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="10" t="n">
         <v>86.5</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>180</v>
+      <c r="H13" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C14" s="8" t="n">
+      <c r="A14" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="9" t="n">
         <v>146</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>41.8</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>180</v>
+      <c r="H14" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C15" s="8" t="n">
+      <c r="A15" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C15" s="9" t="n">
         <v>154</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>41.6</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="10" t="n">
         <v>80.9</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>180</v>
+      <c r="H15" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C16" s="8" t="n">
+      <c r="A16" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" s="9" t="n">
         <v>156</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="10" t="n">
         <v>87.1</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>180</v>
+      <c r="H16" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C17" s="8" t="n">
+      <c r="A17" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="9" t="n">
         <v>154</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>40.3</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="10" t="n">
         <v>83.8</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>180</v>
+      <c r="H17" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="C18" s="8" t="n">
+      <c r="A18" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="10" t="n">
         <v>83.1</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>180</v>
+      <c r="H18" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C19" s="8" t="n">
+      <c r="A19" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>180</v>
+      <c r="H19" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C20" s="8" t="n">
+      <c r="A20" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>38.2</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="10" t="n">
         <v>82.4</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>180</v>
+      <c r="H20" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21" s="8" t="n">
+      <c r="A21" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" s="9" t="n">
         <v>143</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>37.8</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="10" t="n">
         <v>82.1</v>
       </c>
-      <c r="H21" s="7" t="s">
-        <v>180</v>
+      <c r="H21" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C22" s="8" t="n">
+      <c r="A22" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="10" t="n">
         <v>37.5</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="10" t="n">
         <v>89.7</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>180</v>
+      <c r="H22" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" s="8" t="n">
+      <c r="A23" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C23" s="9" t="n">
         <v>115</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="10" t="n">
         <v>37.4</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="10" t="n">
         <v>82.2</v>
       </c>
-      <c r="H23" s="7" t="s">
-        <v>180</v>
+      <c r="H23" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C24" s="8" t="n">
+      <c r="A24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C24" s="9" t="n">
         <v>129</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>37.2</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="10" t="n">
         <v>84.7</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>180</v>
+      <c r="H24" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C25" s="8" t="n">
+      <c r="A25" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" s="9" t="n">
         <v>149</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>36.2</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="10" t="n">
         <v>79.6</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>180</v>
+      <c r="H25" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C26" s="8" t="n">
+      <c r="A26" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="9" t="n">
         <v>126</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>35.7</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="10" t="n">
         <v>77.8</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>180</v>
+      <c r="H26" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C27" s="8" t="n">
+      <c r="A27" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>115</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>35.7</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="10" t="n">
         <v>87.5</v>
       </c>
-      <c r="H27" s="7" t="s">
-        <v>180</v>
+      <c r="H27" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C28" s="8" t="n">
+      <c r="A28" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" s="9" t="n">
         <v>158</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="10" t="n">
         <v>35.4</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="10" t="n">
         <v>82.1</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>180</v>
+      <c r="H28" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="8" t="n">
+      <c r="A29" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="9" t="n">
         <v>144</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="10" t="n">
         <v>35.4</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="10" t="n">
         <v>79.7</v>
       </c>
-      <c r="H29" s="7" t="s">
-        <v>180</v>
+      <c r="H29" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C30" s="8" t="n">
+      <c r="A30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="10" t="n">
         <v>86.6</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>180</v>
+      <c r="H30" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C31" s="8" t="n">
+      <c r="A31" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" s="9" t="n">
         <v>134</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="10" t="n">
         <v>33.6</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="10" t="n">
         <v>83.2</v>
       </c>
-      <c r="H31" s="7" t="s">
-        <v>180</v>
+      <c r="H31" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C32" s="8" t="n">
+      <c r="A32" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" s="9" t="n">
         <v>141</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="10" t="n">
         <v>79.8</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>180</v>
+      <c r="H32" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C33" s="8" t="n">
+      <c r="A33" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C33" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="10" t="n">
         <v>85.5</v>
       </c>
-      <c r="H33" s="7" t="s">
-        <v>180</v>
+      <c r="H33" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C34" s="8" t="n">
+      <c r="A34" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C34" s="9" t="n">
         <v>109</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="10" t="n">
         <v>30.3</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="10" t="n">
         <v>84.2</v>
       </c>
-      <c r="H34" s="7" t="s">
-        <v>180</v>
+      <c r="H34" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C35" s="8" t="n">
+      <c r="A35" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C35" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="10" t="n">
         <v>79.9</v>
       </c>
-      <c r="H35" s="7" t="s">
-        <v>180</v>
+      <c r="H35" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C36" s="8" t="n">
+      <c r="A36" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C36" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="10" t="n">
         <v>88.8</v>
       </c>
-      <c r="H36" s="7" t="s">
-        <v>180</v>
+      <c r="H36" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C37" s="8" t="n">
+      <c r="A37" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C37" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="10" t="n">
         <v>86.6</v>
       </c>
-      <c r="H37" s="7" t="s">
-        <v>180</v>
+      <c r="H37" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C38" s="8" t="n">
+      <c r="A38" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C38" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="10" t="n">
         <v>82.5</v>
       </c>
-      <c r="H38" s="7" t="s">
-        <v>180</v>
+      <c r="H38" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C39" s="8" t="n">
+      <c r="A39" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C39" s="9" t="n">
         <v>109</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="10" t="n">
         <v>81.7</v>
       </c>
-      <c r="H39" s="7" t="s">
-        <v>180</v>
+      <c r="H39" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C40" s="8" t="n">
+      <c r="A40" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C40" s="9" t="n">
         <v>105</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="10" t="n">
         <v>85.4</v>
       </c>
-      <c r="H40" s="7" t="s">
-        <v>180</v>
+      <c r="H40" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C41" s="8" t="n">
+      <c r="A41" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C41" s="9" t="n">
         <v>115</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="10" t="n">
         <v>83.8</v>
       </c>
-      <c r="H41" s="7" t="s">
-        <v>180</v>
+      <c r="H41" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C42" s="8" t="n">
+      <c r="A42" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C42" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="10" t="n">
         <v>81.3</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>180</v>
+      <c r="H42" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C43" s="8" t="n">
+      <c r="A43" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C43" s="9" t="n">
         <v>124</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="G43" s="10" t="n">
         <v>87.4</v>
       </c>
-      <c r="H43" s="7" t="s">
-        <v>180</v>
+      <c r="H43" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="C44" s="8" t="n">
+      <c r="A44" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C44" s="9" t="n">
         <v>103</v>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="G44" s="10" t="n">
         <v>83.6</v>
       </c>
-      <c r="H44" s="7" t="s">
-        <v>180</v>
+      <c r="H44" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C45" s="8" t="n">
+      <c r="A45" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C45" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="G45" s="10" t="n">
         <v>83.8</v>
       </c>
-      <c r="H45" s="7" t="s">
-        <v>180</v>
+      <c r="H45" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C46" s="8" t="n">
+      <c r="A46" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C46" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>11.5</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="10" t="n">
         <v>87.2</v>
       </c>
-      <c r="H46" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>236</v>
+      <c r="H46" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2997,136 +3656,175 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
     <col min="1" max="1" width="34.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="B10" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="B11" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="B14" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B16" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3147,79 +3845,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -3252,18 +3950,18 @@
         <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -3318,18 +4016,18 @@
         <v>73</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -3340,29 +4038,29 @@
         <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -3395,40 +4093,40 @@
         <v>91</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
@@ -3440,6 +4138,17 @@
       </c>
       <c r="C27" s="1" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3449,6 +4158,121 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="125.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3462,233 +4286,238 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>103</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>113</v>
+      <c r="A5" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>118</v>
+      <c r="A6" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>123</v>
+      <c r="A7" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>128</v>
+      <c r="A8" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>133</v>
+      <c r="A9" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>123</v>
+      <c r="A10" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>123</v>
+      <c r="A11" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>154</v>
+      <c r="A14" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>159</v>
+      <c r="A15" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>163</v>
+      <c r="A16" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3697,7 +4526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3710,113 +4539,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>165</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="7" t="n">
+      <c r="A5" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="8" t="n">
         <v>5622</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>5622</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>5622</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="7" t="n">
+      <c r="A6" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="8" t="n">
         <v>2079</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <v>1965</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>2197</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>39.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="7" t="n">
+      <c r="A8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="8" t="n">
         <v>346</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>328</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>366</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="8" t="n">
         <v>1849</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="7" t="n">
+      <c r="A10" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="8" t="n">
         <v>152</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="7" t="n">
+      <c r="A11" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>18432</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>18432</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>18432</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>11.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3824,7 +4686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3844,187 +4706,192 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>176</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>1610</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>180</v>
+      <c r="K5" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>2028</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>313</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>425</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>242</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>180</v>
+      <c r="K6" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="8" t="n">
+      <c r="A7" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>1335</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>1004</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>946</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>1057</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>75.2</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>964</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="10" t="n">
         <v>48.3</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>180</v>
+      <c r="K7" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="8" t="n">
+      <c r="A8" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>649</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>641</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>638</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>643</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>98.8</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>640</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>180</v>
+      <c r="K8" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -4033,7 +4900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -4053,117 +4920,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>185</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>3638</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>434</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>381</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>496</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>11.9</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>245</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>180</v>
+      <c r="K5" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>1984</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <v>1645</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>1584</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>1701</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>82.9</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>1604</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="10" t="n">
         <v>79.1</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>180</v>
+      <c r="K6" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -4172,7 +5044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -4192,732 +5064,192 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>189</v>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>1396</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>326</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>375</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>25.1</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>304</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>180</v>
+      <c r="K5" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>1488</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <v>515</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>486</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>546</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>34.6</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>456</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>180</v>
+      <c r="K6" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="8" t="n">
+      <c r="A7" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>1083</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>448</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>424</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>41.4</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>403</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>180</v>
+      <c r="K7" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="8" t="n">
+      <c r="A8" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>1655</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>765</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>729</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>803</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>46.2</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>685</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="10" t="n">
         <v>36.8</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="9.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.81" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="24.81" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="31.61" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="30.76" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="28.21" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="34.16" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>362</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>172</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>316</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>152</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>146</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>152</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>146</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>159</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>308</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>333</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>314</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>108</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>307</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>289</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>309</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>230</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>233</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>209</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>269</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>277</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -4945,524 +5277,529 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="B5" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>316</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>152</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>146</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>160</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <v>48.2</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J6" s="10" t="n">
         <v>7.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="8" t="n">
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>336</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>152</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>159</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>308</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>148</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>141</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>156</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <v>48.2</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J8" s="10" t="n">
         <v>7.1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>336</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>152</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>146</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>159</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>333</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>156</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>314</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>307</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>230</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>269</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="J18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>362</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>172</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>333</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>156</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>209</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>230</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>233</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>211</v>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="E19" s="9" t="n">
+        <v>277</v>
+      </c>
+      <c r="F19" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G19" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="H14" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="J14" s="9" t="n">
+      <c r="H19" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J19" s="10" t="n">
         <v>3.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>314</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>108</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>289</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>307</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>111</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>269</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>309</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>4.9</v>
       </c>
     </row>
   </sheetData>
